--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/earthwork_designer_main/outputs/019fe51b-bcd3-79d3-bc33-42d91bb2618e/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A69DCD2-2A6E-6B49-8B9F-C6D4CB206972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA5CAA3-A648-B448-92B4-C747E75EB8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,9 +38,6 @@
     <t>3&amp;4%8XKLU7NSN5</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
     <t>Earthwork Designer Licence Registry</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>A public workbook is suitable for basic access control, not high-security licensing.</t>
+  </si>
+  <si>
+    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -574,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
@@ -724,7 +724,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -732,50 +732,50 @@
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
       <c r="A3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1">
       <c r="A4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="32" customHeight="1">
       <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="32" customHeight="1">
       <c r="A6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" customHeight="1">
       <c r="A7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA5CAA3-A648-B448-92B4-C747E75EB8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E590EE78-191F-724B-B76A-C8DA93BE722B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>License_ID</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Inactive</t>
+  </si>
+  <si>
+    <t>Active</t>
   </si>
 </sst>
 </file>
@@ -141,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -250,11 +253,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF17365D"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -300,6 +323,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -342,7 +374,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C3" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token"/>
@@ -578,9 +610,15 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
       <c r="A4" s="3"/>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E590EE78-191F-724B-B76A-C8DA93BE722B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01BFE97-748F-1642-A2A2-F119327CB8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>License_ID</t>
   </si>
@@ -77,10 +77,13 @@
     <t>A public workbook is suitable for basic access control, not high-security licensing.</t>
   </si>
   <si>
-    <t>Inactive</t>
-  </si>
-  <si>
     <t>Active</t>
+  </si>
+  <si>
+    <t>9640920173</t>
+  </si>
+  <si>
+    <t>3&amp;4%8XKLU7NSN6</t>
   </si>
 </sst>
 </file>
@@ -321,17 +324,17 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,14 +613,14 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
-      <c r="A3" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="18" t="s">
+      <c r="A3" s="15" t="s">
         <v>19</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
@@ -761,12 +764,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
       <c r="A3" s="9" t="s">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01BFE97-748F-1642-A2A2-F119327CB8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A6AAF8-7D5D-CE4C-97EA-E452224E4BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,9 +35,6 @@
     <t>9640920172</t>
   </si>
   <si>
-    <t>3&amp;4%8XKLU7NSN5</t>
-  </si>
-  <si>
     <t>Earthwork Designer Licence Registry</t>
   </si>
   <si>
@@ -83,7 +80,10 @@
     <t>9640920173</t>
   </si>
   <si>
-    <t>3&amp;4%8XKLU7NSN6</t>
+    <t xml:space="preserve"> ea:1d:99:cf:f1:7b</t>
+  </si>
+  <si>
+    <t>ba:1e:98:cz:f1:8n</t>
   </si>
 </sst>
 </file>
@@ -147,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -257,9 +257,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF17365D"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFD9E2F3"/>
@@ -267,20 +265,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD9E2F3"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -324,13 +313,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -340,7 +323,69 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -379,8 +424,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C3" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -602,25 +647,25 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="22" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1">
-      <c r="A3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>18</v>
+      <c r="C3" s="15" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
@@ -735,10 +780,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C25">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$C2="Active"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$C2="Inactive"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -764,59 +809,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1">
-      <c r="A1" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="A1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
       <c r="A3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1">
       <c r="A4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="32" customHeight="1">
       <c r="A5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="32" customHeight="1">
       <c r="A6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" customHeight="1">
       <c r="A7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A6AAF8-7D5D-CE4C-97EA-E452224E4BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD8D129-EE55-F942-BDE8-A88C5CA78903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>ba:1e:98:cz:f1:8n</t>
+  </si>
+  <si>
+    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -326,6 +329,28 @@
   <dxfs count="4">
     <dxf>
       <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -386,28 +411,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -424,8 +427,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C3" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -654,7 +657,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
@@ -780,10 +783,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C25">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$C2="Active"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$C2="Inactive"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD8D129-EE55-F942-BDE8-A88C5CA78903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06D5279-2BBD-6F4B-9786-2B3BB01D99D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>ba:1e:98:cz:f1:8n</t>
-  </si>
-  <si>
-    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -657,7 +654,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06D5279-2BBD-6F4B-9786-2B3BB01D99D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943310C9-6EDE-194E-9210-99F4BA03472A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>ba:1e:98:cz:f1:8n</t>
+  </si>
+  <si>
+    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943310C9-6EDE-194E-9210-99F4BA03472A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4726E0A-4A75-B242-B5B2-5ADDC0783E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>ba:1e:98:cz:f1:8n</t>
-  </si>
-  <si>
-    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -657,7 +654,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4726E0A-4A75-B242-B5B2-5ADDC0783E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47879D7-ACD8-F24A-B1A0-7268731E2BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>ba:1e:98:cz:f1:8n</t>
+  </si>
+  <si>
+    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47879D7-ACD8-F24A-B1A0-7268731E2BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF6FAC0-F5A9-7443-9B74-371AD5D95049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>ba:1e:98:cz:f1:8n</t>
-  </si>
-  <si>
-    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -657,7 +654,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF6FAC0-F5A9-7443-9B74-371AD5D95049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8754AC-60EF-F841-AE96-0E04FB1B63FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
     <t xml:space="preserve"> ea:1d:99:cf:f1:7b</t>
   </si>
   <si>
-    <t>ba:1e:98:cz:f1:8n</t>
+    <t>14-13-33-5E-F9-6D</t>
   </si>
 </sst>
 </file>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8754AC-60EF-F841-AE96-0E04FB1B63FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7DDBB4-3465-F54C-B71C-05E946E4510B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>14-13-33-5E-F9-6D</t>
+  </si>
+  <si>
+    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -665,7 +668,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7DDBB4-3465-F54C-B71C-05E946E4510B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A80BD2-E253-F94A-A81C-E891A6B62ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>License_ID</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>14-13-33-5E-F9-6D</t>
-  </si>
-  <si>
-    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -668,7 +665,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A80BD2-E253-F94A-A81C-E891A6B62ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4CDCBD-9179-DB41-8DD5-DE467EF86558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
     <t xml:space="preserve"> ea:1d:99:cf:f1:7b</t>
   </si>
   <si>
-    <t>14-13-33-5E-F9-6D</t>
+    <t>14-13-33-5E-F9-6C</t>
   </si>
 </sst>
 </file>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4CDCBD-9179-DB41-8DD5-DE467EF86558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E420FB-D649-1F4E-A4F6-2EE03F3334D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>License_ID</t>
   </si>
@@ -83,7 +83,13 @@
     <t xml:space="preserve"> ea:1d:99:cf:f1:7b</t>
   </si>
   <si>
-    <t>14-13-33-5E-F9-6C</t>
+    <t>8084928629</t>
+  </si>
+  <si>
+    <t>50-5B-C2-EE-1A-89</t>
+  </si>
+  <si>
+    <t>14-13-33-5E-F9-6E</t>
   </si>
 </sst>
 </file>
@@ -269,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -318,6 +324,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -422,7 +431,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C3" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C4" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token" dataDxfId="2"/>
@@ -662,16 +671,22 @@
         <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1">
       <c r="A5" s="3"/>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E420FB-D649-1F4E-A4F6-2EE03F3334D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED928DFD-BE57-AA43-8ED1-A94155B5070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,7 +89,7 @@
     <t>50-5B-C2-EE-1A-89</t>
   </si>
   <si>
-    <t>14-13-33-5E-F9-6E</t>
+    <t>14-13-33-5E-F9-6D</t>
   </si>
 </sst>
 </file>
@@ -322,11 +322,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,10 +678,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -824,12 +824,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
       <c r="A3" s="9" t="s">

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED928DFD-BE57-AA43-8ED1-A94155B5070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BFCA25-4DB1-B54B-9A1C-DB6D1350346B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>License_ID</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>14-13-33-5E-F9-6D</t>
+  </si>
+  <si>
+    <t>7903474096</t>
+  </si>
+  <si>
+    <t>00-50-56-C0-00-08</t>
   </si>
 </sst>
 </file>
@@ -431,7 +437,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C4" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C5" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token" dataDxfId="2"/>
@@ -689,9 +695,15 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
+      <c r="A5" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="22" customHeight="1">
       <c r="A6" s="3"/>

--- a/license_registry.xlsx
+++ b/license_registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BFCA25-4DB1-B54B-9A1C-DB6D1350346B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D389B7-84B9-AB42-835C-18CC248E93E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,9 +80,6 @@
     <t>9640920173</t>
   </si>
   <si>
-    <t xml:space="preserve"> ea:1d:99:cf:f1:7b</t>
-  </si>
-  <si>
     <t>8084928629</t>
   </si>
   <si>
@@ -96,6 +93,9 @@
   </si>
   <si>
     <t>00-50-56-C0-00-08</t>
+  </si>
+  <si>
+    <t>14:7f:ce:e0:91:d8</t>
   </si>
 </sst>
 </file>
@@ -666,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
@@ -677,7 +677,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>17</v>
@@ -685,10 +685,10 @@
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
       <c r="A4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>21</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>17</v>
@@ -696,10 +696,10 @@
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1">
       <c r="A5" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>24</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>17</v>
